--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/104.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/104.xlsx
@@ -426,13 +426,13 @@
         <v>-39.95600885426017</v>
       </c>
       <c r="E2">
-        <v>-10.55470398372336</v>
+        <v>-11.32277812008053</v>
       </c>
       <c r="F2">
-        <v>0.558071800385922</v>
+        <v>1.303874167413595</v>
       </c>
       <c r="G2">
-        <v>-17.922298972031</v>
+        <v>-21.89025284524363</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-38.87991627547446</v>
       </c>
       <c r="E3">
-        <v>-10.2563912738949</v>
+        <v>-11.92034216549686</v>
       </c>
       <c r="F3">
-        <v>-0.245851308724373</v>
+        <v>1.649823589109947</v>
       </c>
       <c r="G3">
-        <v>-17.45711258466955</v>
+        <v>-21.2027713462411</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-37.5678605580453</v>
       </c>
       <c r="E4">
-        <v>-10.72010147152334</v>
+        <v>-12.73750310650218</v>
       </c>
       <c r="F4">
-        <v>0.2342662961012064</v>
+        <v>1.034939719890319</v>
       </c>
       <c r="G4">
-        <v>-16.21634577476459</v>
+        <v>-20.73989677321508</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-36.17274303925203</v>
       </c>
       <c r="E5">
-        <v>-11.35928484762577</v>
+        <v>-13.18675182229755</v>
       </c>
       <c r="F5">
-        <v>0.5007935079519473</v>
+        <v>1.805301523676192</v>
       </c>
       <c r="G5">
-        <v>-15.84696718703552</v>
+        <v>-20.19359455140773</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-34.75951082930329</v>
       </c>
       <c r="E6">
-        <v>-12.704871325123</v>
+        <v>-14.13952341948117</v>
       </c>
       <c r="F6">
-        <v>-0.1882085346331666</v>
+        <v>2.166804371727507</v>
       </c>
       <c r="G6">
-        <v>-15.63564307685245</v>
+        <v>-19.50155860846601</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-33.39545469777756</v>
       </c>
       <c r="E7">
-        <v>-13.6979373785801</v>
+        <v>-14.98277483402906</v>
       </c>
       <c r="F7">
-        <v>0.7241528377080004</v>
+        <v>1.606425420877281</v>
       </c>
       <c r="G7">
-        <v>-15.91563629664328</v>
+        <v>-19.09688079580664</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-32.14218480210402</v>
       </c>
       <c r="E8">
-        <v>-13.81447648835479</v>
+        <v>-15.19684795855602</v>
       </c>
       <c r="F8">
-        <v>0.6729083734360174</v>
+        <v>2.028233415852401</v>
       </c>
       <c r="G8">
-        <v>-14.50931695072665</v>
+        <v>-17.85090163432553</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-31.01968800708121</v>
       </c>
       <c r="E9">
-        <v>-13.62521880149368</v>
+        <v>-16.01362680411945</v>
       </c>
       <c r="F9">
-        <v>0.3400115369055773</v>
+        <v>1.808856876569007</v>
       </c>
       <c r="G9">
-        <v>-15.04504304619539</v>
+        <v>-17.02109474125231</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-30.05013217984909</v>
       </c>
       <c r="E10">
-        <v>-14.89346417769995</v>
+        <v>-17.12157068282131</v>
       </c>
       <c r="F10">
-        <v>0.8283796810630398</v>
+        <v>2.102774884960717</v>
       </c>
       <c r="G10">
-        <v>-13.08482421171128</v>
+        <v>-16.38966527593483</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-29.21066496827307</v>
       </c>
       <c r="E11">
-        <v>-16.31042359181435</v>
+        <v>-17.52739342100428</v>
       </c>
       <c r="F11">
-        <v>0.3002416178971731</v>
+        <v>2.24934289974245</v>
       </c>
       <c r="G11">
-        <v>-13.07273254813754</v>
+        <v>-15.79031402940836</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-28.49842589592795</v>
       </c>
       <c r="E12">
-        <v>-16.68259701184356</v>
+        <v>-17.91107538961459</v>
       </c>
       <c r="F12">
-        <v>1.363012973034258</v>
+        <v>2.42209395139187</v>
       </c>
       <c r="G12">
-        <v>-13.29909846328231</v>
+        <v>-15.07674792850987</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-27.87318441311005</v>
       </c>
       <c r="E13">
-        <v>-17.51075150322569</v>
+        <v>-18.91770583125859</v>
       </c>
       <c r="F13">
-        <v>0.7788134891491286</v>
+        <v>2.545123078055653</v>
       </c>
       <c r="G13">
-        <v>-11.3761310379965</v>
+        <v>-14.12693554956154</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-27.31913792518721</v>
       </c>
       <c r="E14">
-        <v>-17.97951615903644</v>
+        <v>-20.67441454458926</v>
       </c>
       <c r="F14">
-        <v>1.615486103529102</v>
+        <v>2.830621560165308</v>
       </c>
       <c r="G14">
-        <v>-10.28191837571369</v>
+        <v>-13.16115063520477</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-26.78749292756072</v>
       </c>
       <c r="E15">
-        <v>-18.17080891944672</v>
+        <v>-21.76515997519501</v>
       </c>
       <c r="F15">
-        <v>1.773531977044025</v>
+        <v>2.901775006596174</v>
       </c>
       <c r="G15">
-        <v>-10.81599709134544</v>
+        <v>-12.67735094428098</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-26.24146776225836</v>
       </c>
       <c r="E16">
-        <v>-20.75298084322105</v>
+        <v>-21.30247977397514</v>
       </c>
       <c r="F16">
-        <v>1.555677977046978</v>
+        <v>2.949520446958732</v>
       </c>
       <c r="G16">
-        <v>-9.046362612012599</v>
+        <v>-11.74278270300015</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-25.63461945701507</v>
       </c>
       <c r="E17">
-        <v>-23.20871655463361</v>
+        <v>-22.94893733947691</v>
       </c>
       <c r="F17">
-        <v>1.853474401618594</v>
+        <v>3.382363952473947</v>
       </c>
       <c r="G17">
-        <v>-9.241501411103066</v>
+        <v>-11.43540146707625</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-24.93465035189557</v>
       </c>
       <c r="E18">
-        <v>-22.55405000671222</v>
+        <v>-23.53093930205911</v>
       </c>
       <c r="F18">
-        <v>2.522531842246505</v>
+        <v>3.247994476065839</v>
       </c>
       <c r="G18">
-        <v>-8.560025277346243</v>
+        <v>-11.7631856719797</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-24.12260525953077</v>
       </c>
       <c r="E19">
-        <v>-22.70372343643639</v>
+        <v>-24.45085899766334</v>
       </c>
       <c r="F19">
-        <v>2.057015869630072</v>
+        <v>3.54985487111559</v>
       </c>
       <c r="G19">
-        <v>-8.985972173503262</v>
+        <v>-10.85564777482297</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-23.18960853146224</v>
       </c>
       <c r="E20">
-        <v>-23.57448156958861</v>
+        <v>-25.55130632992388</v>
       </c>
       <c r="F20">
-        <v>1.381013396697091</v>
+        <v>3.531658952745696</v>
       </c>
       <c r="G20">
-        <v>-7.637771918301701</v>
+        <v>-10.27212677812472</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-22.15119616038657</v>
       </c>
       <c r="E21">
-        <v>-24.47180779558577</v>
+        <v>-26.37779123035343</v>
       </c>
       <c r="F21">
-        <v>1.276610939452658</v>
+        <v>3.63278604527946</v>
       </c>
       <c r="G21">
-        <v>-8.657030103373648</v>
+        <v>-9.759128519693915</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-21.02488143724805</v>
       </c>
       <c r="E22">
-        <v>-23.64354116749786</v>
+        <v>-25.75604303539263</v>
       </c>
       <c r="F22">
-        <v>1.878491097183139</v>
+        <v>3.653437244631252</v>
       </c>
       <c r="G22">
-        <v>-7.158437906001007</v>
+        <v>-9.068719723318598</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-19.85548900865568</v>
       </c>
       <c r="E23">
-        <v>-24.3294440177933</v>
+        <v>-27.10354829652192</v>
       </c>
       <c r="F23">
-        <v>2.081035210841647</v>
+        <v>3.685579556594678</v>
       </c>
       <c r="G23">
-        <v>-7.59008014148354</v>
+        <v>-9.463861138672776</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-18.67751697123608</v>
       </c>
       <c r="E24">
-        <v>-24.66818823986896</v>
+        <v>-25.96794818360803</v>
       </c>
       <c r="F24">
-        <v>2.109822634823735</v>
+        <v>3.458111524520739</v>
       </c>
       <c r="G24">
-        <v>-7.962462390864688</v>
+        <v>-9.127484973319968</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-17.55073122238449</v>
       </c>
       <c r="E25">
-        <v>-26.96023758654739</v>
+        <v>-27.60413485750351</v>
       </c>
       <c r="F25">
-        <v>2.36204725509774</v>
+        <v>3.567991147032482</v>
       </c>
       <c r="G25">
-        <v>-7.285528952696401</v>
+        <v>-8.750347252666106</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-16.51425691713381</v>
       </c>
       <c r="E26">
-        <v>-24.83675462790978</v>
+        <v>-26.95466813016079</v>
       </c>
       <c r="F26">
-        <v>1.861479744199249</v>
+        <v>3.360622621620071</v>
       </c>
       <c r="G26">
-        <v>-7.557957540034482</v>
+        <v>-8.970857267693011</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-15.62623096558693</v>
       </c>
       <c r="E27">
-        <v>-25.07617480115217</v>
+        <v>-26.92794221528552</v>
       </c>
       <c r="F27">
-        <v>1.903903752366223</v>
+        <v>2.994898413284089</v>
       </c>
       <c r="G27">
-        <v>-6.098801945082902</v>
+        <v>-9.518480526263456</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-14.91451822883154</v>
       </c>
       <c r="E28">
-        <v>-23.80832398002176</v>
+        <v>-26.70591984428284</v>
       </c>
       <c r="F28">
-        <v>1.510497162163487</v>
+        <v>2.81334181614291</v>
       </c>
       <c r="G28">
-        <v>-6.741984982549571</v>
+        <v>-9.059413724223575</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-14.41653750479208</v>
       </c>
       <c r="E29">
-        <v>-23.02338780568579</v>
+        <v>-25.94416689556206</v>
       </c>
       <c r="F29">
-        <v>1.305984847555928</v>
+        <v>2.50650458973714</v>
       </c>
       <c r="G29">
-        <v>-8.532727331901562</v>
+        <v>-8.559110211367058</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-14.13796208610802</v>
       </c>
       <c r="E30">
-        <v>-23.94557930788469</v>
+        <v>-25.72932958015133</v>
       </c>
       <c r="F30">
-        <v>1.986394235071803</v>
+        <v>2.568940297620944</v>
       </c>
       <c r="G30">
-        <v>-6.984619752613867</v>
+        <v>-8.31475757136181</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-14.0880208243194</v>
       </c>
       <c r="E31">
-        <v>-22.47387641529772</v>
+        <v>-26.03058276359777</v>
       </c>
       <c r="F31">
-        <v>1.844635721430724</v>
+        <v>2.448959562999464</v>
       </c>
       <c r="G31">
-        <v>-6.603699063047483</v>
+        <v>-8.13648287695764</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-14.25346126253787</v>
       </c>
       <c r="E32">
-        <v>-23.62406675959574</v>
+        <v>-24.88755255562376</v>
       </c>
       <c r="F32">
-        <v>2.125248492598668</v>
+        <v>2.268905624326963</v>
       </c>
       <c r="G32">
-        <v>-7.123122363917018</v>
+        <v>-9.180994794459425</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-14.61743464172877</v>
       </c>
       <c r="E33">
-        <v>-21.46113244658358</v>
+        <v>-23.99820049537027</v>
       </c>
       <c r="F33">
-        <v>1.874746876522486</v>
+        <v>2.274810227174118</v>
       </c>
       <c r="G33">
-        <v>-7.500408897012572</v>
+        <v>-9.022305905977786</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-15.15540748227184</v>
       </c>
       <c r="E34">
-        <v>-23.05182069041557</v>
+        <v>-23.17121720958174</v>
       </c>
       <c r="F34">
-        <v>1.293826070817637</v>
+        <v>2.683344462886778</v>
       </c>
       <c r="G34">
-        <v>-7.11644407925295</v>
+        <v>-8.332368349001165</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-15.83139030831891</v>
       </c>
       <c r="E35">
-        <v>-23.54658029590842</v>
+        <v>-23.25450986270117</v>
       </c>
       <c r="F35">
-        <v>1.54199334755273</v>
+        <v>2.366573454586636</v>
       </c>
       <c r="G35">
-        <v>-7.949214167437083</v>
+        <v>-8.651877798923087</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-16.61630237429221</v>
       </c>
       <c r="E36">
-        <v>-21.86022282920901</v>
+        <v>-22.00542325033634</v>
       </c>
       <c r="F36">
-        <v>1.964992534853075</v>
+        <v>2.602565387235382</v>
       </c>
       <c r="G36">
-        <v>-8.36173269878971</v>
+        <v>-9.262083216087108</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-17.46457925164808</v>
       </c>
       <c r="E37">
-        <v>-19.39072752867728</v>
+        <v>-21.33871238957294</v>
       </c>
       <c r="F37">
-        <v>1.873668342164041</v>
+        <v>3.014141388051122</v>
       </c>
       <c r="G37">
-        <v>-7.970609219361257</v>
+        <v>-9.816951290897892</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-18.3486080786326</v>
       </c>
       <c r="E38">
-        <v>-19.074261132148</v>
+        <v>-20.30340402373101</v>
       </c>
       <c r="F38">
-        <v>1.481605363888646</v>
+        <v>2.730596196277268</v>
       </c>
       <c r="G38">
-        <v>-7.361720922843451</v>
+        <v>-9.410635888693749</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-19.22336922079268</v>
       </c>
       <c r="E39">
-        <v>-19.42233762007055</v>
+        <v>-20.36506675227074</v>
       </c>
       <c r="F39">
-        <v>1.815084542703254</v>
+        <v>2.914550088682148</v>
       </c>
       <c r="G39">
-        <v>-7.190132345337122</v>
+        <v>-9.629369292026404</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-20.06867540235125</v>
       </c>
       <c r="E40">
-        <v>-17.29267052977027</v>
+        <v>-19.33401127482542</v>
       </c>
       <c r="F40">
-        <v>2.105339510439784</v>
+        <v>2.921241640561963</v>
       </c>
       <c r="G40">
-        <v>-8.720066531526079</v>
+        <v>-9.739666724139461</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-20.84969550583995</v>
       </c>
       <c r="E41">
-        <v>-17.23842543665669</v>
+        <v>-18.71896220973156</v>
       </c>
       <c r="F41">
-        <v>2.296679126608025</v>
+        <v>3.262734445631253</v>
       </c>
       <c r="G41">
-        <v>-8.869470306869424</v>
+        <v>-10.81426094619235</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-21.55952124262699</v>
       </c>
       <c r="E42">
-        <v>-16.3635597775042</v>
+        <v>-18.985220434555</v>
       </c>
       <c r="F42">
-        <v>2.543453089371609</v>
+        <v>3.320208232772289</v>
       </c>
       <c r="G42">
-        <v>-9.257118885247106</v>
+        <v>-10.46538845185418</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-22.17916029454744</v>
       </c>
       <c r="E43">
-        <v>-15.9741920625902</v>
+        <v>-17.21602716798189</v>
       </c>
       <c r="F43">
-        <v>2.119164962392508</v>
+        <v>3.314234047063298</v>
       </c>
       <c r="G43">
-        <v>-10.13968631576213</v>
+        <v>-10.88050075795808</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-22.71521547216815</v>
       </c>
       <c r="E44">
-        <v>-16.63467310636636</v>
+        <v>-18.19843608117948</v>
       </c>
       <c r="F44">
-        <v>2.859461999661176</v>
+        <v>3.462788486876945</v>
       </c>
       <c r="G44">
-        <v>-9.795874749813835</v>
+        <v>-11.30357452969258</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-23.16369760386828</v>
       </c>
       <c r="E45">
-        <v>-14.12374121644682</v>
+        <v>-16.13791165301495</v>
       </c>
       <c r="F45">
-        <v>2.163729471928316</v>
+        <v>3.561785018450708</v>
       </c>
       <c r="G45">
-        <v>-7.851069751395657</v>
+        <v>-11.47083579803913</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-23.54079776461841</v>
       </c>
       <c r="E46">
-        <v>-16.22452272198292</v>
+        <v>-15.39974063819654</v>
       </c>
       <c r="F46">
-        <v>2.128086479320658</v>
+        <v>3.551205109982153</v>
       </c>
       <c r="G46">
-        <v>-10.2463665612442</v>
+        <v>-12.01945766641568</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-23.85173502219427</v>
       </c>
       <c r="E47">
-        <v>-14.90934190459476</v>
+        <v>-15.21507224984937</v>
       </c>
       <c r="F47">
-        <v>2.138091500811671</v>
+        <v>3.978264954291022</v>
       </c>
       <c r="G47">
-        <v>-10.09133402056242</v>
+        <v>-12.7760827778554</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-24.11362861459647</v>
       </c>
       <c r="E48">
-        <v>-14.16355390020663</v>
+        <v>-15.0023032336784</v>
       </c>
       <c r="F48">
-        <v>2.215229073360361</v>
+        <v>3.577659851357958</v>
       </c>
       <c r="G48">
-        <v>-10.50429768386783</v>
+        <v>-12.37082603258296</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-24.33282969294873</v>
       </c>
       <c r="E49">
-        <v>-13.23767434635128</v>
+        <v>-14.57761245644673</v>
       </c>
       <c r="F49">
-        <v>2.483784128613155</v>
+        <v>4.018260189232987</v>
       </c>
       <c r="G49">
-        <v>-10.35288494056163</v>
+        <v>-12.84046635021685</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-24.52065887132536</v>
       </c>
       <c r="E50">
-        <v>-11.30502729487821</v>
+        <v>-13.38411242445341</v>
       </c>
       <c r="F50">
-        <v>1.92777895764971</v>
+        <v>3.844162212186615</v>
       </c>
       <c r="G50">
-        <v>-10.54674316943015</v>
+        <v>-12.88917762279784</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-24.6802223595755</v>
       </c>
       <c r="E51">
-        <v>-13.05641574450178</v>
+        <v>-13.02042401516082</v>
       </c>
       <c r="F51">
-        <v>2.274742301047089</v>
+        <v>3.42756630490991</v>
       </c>
       <c r="G51">
-        <v>-10.66296699176504</v>
+        <v>-13.18580259100636</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-24.81492106812104</v>
       </c>
       <c r="E52">
-        <v>-11.63517021630016</v>
+        <v>-12.2669110377085</v>
       </c>
       <c r="F52">
-        <v>2.293740079062892</v>
+        <v>3.575878861441939</v>
       </c>
       <c r="G52">
-        <v>-10.901294033254</v>
+        <v>-13.43566781821574</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-24.92531904894321</v>
       </c>
       <c r="E53">
-        <v>-10.63798833042015</v>
+        <v>-12.06004373483012</v>
       </c>
       <c r="F53">
-        <v>2.095795061224728</v>
+        <v>3.497775412501585</v>
       </c>
       <c r="G53">
-        <v>-11.52531420542189</v>
+        <v>-13.44542939224191</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-25.0084495283523</v>
       </c>
       <c r="E54">
-        <v>-9.833012911441882</v>
+        <v>-11.45047275547371</v>
       </c>
       <c r="F54">
-        <v>2.858578960009791</v>
+        <v>3.714791104686999</v>
       </c>
       <c r="G54">
-        <v>-11.35075329519858</v>
+        <v>-13.73290370065858</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-25.06694103673329</v>
       </c>
       <c r="E55">
-        <v>-10.28385646038599</v>
+        <v>-11.13868287489618</v>
       </c>
       <c r="F55">
-        <v>2.166559174976279</v>
+        <v>3.571735367693136</v>
       </c>
       <c r="G55">
-        <v>-11.3959622539106</v>
+        <v>-13.80865053885285</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-25.09429093913974</v>
       </c>
       <c r="E56">
-        <v>-9.778929793569965</v>
+        <v>-9.685362095632902</v>
       </c>
       <c r="F56">
-        <v>2.68481564339415</v>
+        <v>3.722044289665912</v>
       </c>
       <c r="G56">
-        <v>-11.88026712391277</v>
+        <v>-13.86872116114977</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-25.09465304971444</v>
       </c>
       <c r="E57">
-        <v>-10.42886168058106</v>
+        <v>-10.50261440728736</v>
       </c>
       <c r="F57">
-        <v>2.930229426882337</v>
+        <v>3.422778341321729</v>
       </c>
       <c r="G57">
-        <v>-11.15208607479323</v>
+        <v>-14.06060697247971</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-25.05902439123054</v>
       </c>
       <c r="E58">
-        <v>-10.19997820446976</v>
+        <v>-10.48989727421074</v>
       </c>
       <c r="F58">
-        <v>2.42909199921072</v>
+        <v>3.43035955979215</v>
       </c>
       <c r="G58">
-        <v>-11.40508550088424</v>
+        <v>-14.08197852770257</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-24.99427393041229</v>
       </c>
       <c r="E59">
-        <v>-9.687546684789762</v>
+        <v>-9.559212454852561</v>
       </c>
       <c r="F59">
-        <v>2.294424310537605</v>
+        <v>3.455704288848204</v>
       </c>
       <c r="G59">
-        <v>-12.30933385985617</v>
+        <v>-13.92065539792849</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-24.89255435574108</v>
       </c>
       <c r="E60">
-        <v>-9.39864099861204</v>
+        <v>-8.837517229359754</v>
       </c>
       <c r="F60">
-        <v>2.879811673278348</v>
+        <v>3.69673269530597</v>
       </c>
       <c r="G60">
-        <v>-13.16387103106871</v>
+        <v>-14.0158979713569</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-24.76600335241008</v>
       </c>
       <c r="E61">
-        <v>-10.14253098542473</v>
+        <v>-8.234778282632687</v>
       </c>
       <c r="F61">
-        <v>2.697002584624137</v>
+        <v>3.631157474965556</v>
       </c>
       <c r="G61">
-        <v>-12.78213056770072</v>
+        <v>-14.26933339179463</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-24.60888834966204</v>
       </c>
       <c r="E62">
-        <v>-8.508778093365601</v>
+        <v>-9.218923238164059</v>
       </c>
       <c r="F62">
-        <v>3.298978832973343</v>
+        <v>3.219876372945213</v>
       </c>
       <c r="G62">
-        <v>-12.31677578731314</v>
+        <v>-13.90658740069928</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-24.43757313444461</v>
       </c>
       <c r="E63">
-        <v>-8.272684642394397</v>
+        <v>-8.224760736917201</v>
       </c>
       <c r="F63">
-        <v>2.586720375554633</v>
+        <v>3.191774837172642</v>
       </c>
       <c r="G63">
-        <v>-11.9975365494564</v>
+        <v>-14.39238300586298</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-24.24794273356778</v>
       </c>
       <c r="E64">
-        <v>-6.831412329184448</v>
+        <v>-8.389385727410755</v>
       </c>
       <c r="F64">
-        <v>1.844612527143445</v>
+        <v>3.269522088129793</v>
       </c>
       <c r="G64">
-        <v>-11.57882794267824</v>
+        <v>-13.74229715969741</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-24.05774883965452</v>
       </c>
       <c r="E65">
-        <v>-6.783455198016653</v>
+        <v>-7.802848458061844</v>
       </c>
       <c r="F65">
-        <v>2.52883903165142</v>
+        <v>3.526610881793036</v>
       </c>
       <c r="G65">
-        <v>-12.33702733310641</v>
+        <v>-13.46081712086194</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-23.86208416532153</v>
       </c>
       <c r="E66">
-        <v>-6.523738281029825</v>
+        <v>-8.198146958747699</v>
       </c>
       <c r="F66">
-        <v>1.952904997711425</v>
+        <v>3.481854191019778</v>
       </c>
       <c r="G66">
-        <v>-12.81949946040562</v>
+        <v>-13.82854310726483</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-23.67591134649378</v>
       </c>
       <c r="E67">
-        <v>-8.318656538548925</v>
+        <v>-8.457166136231956</v>
       </c>
       <c r="F67">
-        <v>1.800328005789784</v>
+        <v>2.917060041912631</v>
       </c>
       <c r="G67">
-        <v>-13.39792167291743</v>
+        <v>-13.41165680021127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-23.49232956337373</v>
       </c>
       <c r="E68">
-        <v>-7.973287944410158</v>
+        <v>-7.802159024981923</v>
       </c>
       <c r="F68">
-        <v>1.931740210569897</v>
+        <v>3.319987887043144</v>
       </c>
       <c r="G68">
-        <v>-12.67746842778758</v>
+        <v>-13.99269367343108</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-23.32307135229611</v>
       </c>
       <c r="E69">
-        <v>-6.815306175666763</v>
+        <v>-8.630105855797817</v>
       </c>
       <c r="F69">
-        <v>1.949170717459604</v>
+        <v>3.308679015260125</v>
       </c>
       <c r="G69">
-        <v>-11.32219958160558</v>
+        <v>-13.69006921415219</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-23.16170076194539</v>
       </c>
       <c r="E70">
-        <v>-9.099103091442755</v>
+        <v>-7.887075583729367</v>
       </c>
       <c r="F70">
-        <v>2.728618054919382</v>
+        <v>2.886408791274244</v>
       </c>
       <c r="G70">
-        <v>-11.72113049273376</v>
+        <v>-12.93095997923402</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-23.01727618602396</v>
       </c>
       <c r="E71">
-        <v>-9.201438218486532</v>
+        <v>-8.624092005799465</v>
       </c>
       <c r="F71">
-        <v>2.439605638287052</v>
+        <v>3.032524517454048</v>
       </c>
       <c r="G71">
-        <v>-11.61961168930832</v>
+        <v>-13.01190611528149</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-22.88497577596653</v>
       </c>
       <c r="E72">
-        <v>-6.902045994185808</v>
+        <v>-8.781722988422008</v>
       </c>
       <c r="F72">
-        <v>2.29455022238283</v>
+        <v>2.987867230769127</v>
       </c>
       <c r="G72">
-        <v>-11.36586950638113</v>
+        <v>-12.78388890418283</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-22.77002518373892</v>
       </c>
       <c r="E73">
-        <v>-8.891367767397481</v>
+        <v>-9.355916913713529</v>
       </c>
       <c r="F73">
-        <v>1.868623584680992</v>
+        <v>3.02879355067184</v>
       </c>
       <c r="G73">
-        <v>-13.39095098485915</v>
+        <v>-12.30505354409904</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-22.66896153206228</v>
       </c>
       <c r="E74">
-        <v>-9.469037930567884</v>
+        <v>-9.516941069988455</v>
       </c>
       <c r="F74">
-        <v>1.677681584866095</v>
+        <v>2.976629598582749</v>
       </c>
       <c r="G74">
-        <v>-11.22791384606982</v>
+        <v>-12.18266966990142</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-22.58044886873002</v>
       </c>
       <c r="E75">
-        <v>-9.643560023648504</v>
+        <v>-9.803122249537092</v>
       </c>
       <c r="F75">
-        <v>2.4202682296361</v>
+        <v>3.003773541637683</v>
       </c>
       <c r="G75">
-        <v>-11.95949800076388</v>
+        <v>-12.14982128145603</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-22.49971850558737</v>
       </c>
       <c r="E76">
-        <v>-9.955075792278594</v>
+        <v>-9.487195770480033</v>
       </c>
       <c r="F76">
-        <v>2.622263964073954</v>
+        <v>2.805618118479208</v>
       </c>
       <c r="G76">
-        <v>-11.79073163816054</v>
+        <v>-11.87836911259503</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-22.41562039994526</v>
       </c>
       <c r="E77">
-        <v>-9.016558016361788</v>
+        <v>-9.944676151121222</v>
       </c>
       <c r="F77">
-        <v>2.079779405859003</v>
+        <v>2.774019215532018</v>
       </c>
       <c r="G77">
-        <v>-11.25943336551833</v>
+        <v>-11.66991682146218</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-22.32262720498739</v>
       </c>
       <c r="E78">
-        <v>-10.61866343812572</v>
+        <v>-10.32160084490604</v>
       </c>
       <c r="F78">
-        <v>2.450463878202948</v>
+        <v>2.558607242638423</v>
       </c>
       <c r="G78">
-        <v>-11.70818772642331</v>
+        <v>-10.46832945563607</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-22.20509199727477</v>
       </c>
       <c r="E79">
-        <v>-9.225763577216052</v>
+        <v>-10.49380959927873</v>
       </c>
       <c r="F79">
-        <v>1.945057044937302</v>
+        <v>2.68946112778905</v>
       </c>
       <c r="G79">
-        <v>-10.37682546846214</v>
+        <v>-10.50565657642751</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-22.06053645957686</v>
       </c>
       <c r="E80">
-        <v>-11.01129142392971</v>
+        <v>-11.00216266543774</v>
       </c>
       <c r="F80">
-        <v>2.092001138519906</v>
+        <v>2.777203459828379</v>
       </c>
       <c r="G80">
-        <v>-12.00205444297132</v>
+        <v>-10.63360525272108</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-21.87517493460668</v>
       </c>
       <c r="E81">
-        <v>-11.44267302460568</v>
+        <v>-12.62268757942729</v>
       </c>
       <c r="F81">
-        <v>2.423361353518154</v>
+        <v>2.792516659636531</v>
       </c>
       <c r="G81">
-        <v>-9.872646305260112</v>
+        <v>-9.926524241386916</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-21.65431028669596</v>
       </c>
       <c r="E82">
-        <v>-11.18453017471096</v>
+        <v>-12.49702386437195</v>
       </c>
       <c r="F82">
-        <v>2.271379129391723</v>
+        <v>2.707121920816735</v>
       </c>
       <c r="G82">
-        <v>-10.48609035108941</v>
+        <v>-9.783320984447467</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-21.38971950181549</v>
       </c>
       <c r="E83">
-        <v>-12.47931457128288</v>
+        <v>-14.13418654292876</v>
       </c>
       <c r="F83">
-        <v>1.291446999636797</v>
+        <v>2.759782893347506</v>
       </c>
       <c r="G83">
-        <v>-9.740252836300167</v>
+        <v>-9.809401017540393</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-21.09438900326285</v>
       </c>
       <c r="E84">
-        <v>-15.53736144865606</v>
+        <v>-15.06081782803391</v>
       </c>
       <c r="F84">
-        <v>1.706919640715306</v>
+        <v>2.570191132399172</v>
       </c>
       <c r="G84">
-        <v>-9.728684627016943</v>
+        <v>-8.611554848713341</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-20.76555390611341</v>
       </c>
       <c r="E85">
-        <v>-16.33491507899686</v>
+        <v>-15.97466137546991</v>
       </c>
       <c r="F85">
-        <v>1.406936326200299</v>
+        <v>2.66586922415732</v>
       </c>
       <c r="G85">
-        <v>-9.035565877756051</v>
+        <v>-8.80247729528916</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-20.42264732311533</v>
       </c>
       <c r="E86">
-        <v>-16.02606151882599</v>
+        <v>-16.2855583156126</v>
       </c>
       <c r="F86">
-        <v>1.733304799229276</v>
+        <v>2.636496972788855</v>
       </c>
       <c r="G86">
-        <v>-8.947967564490426</v>
+        <v>-9.050624652557591</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-20.06823710970051</v>
       </c>
       <c r="E87">
-        <v>-17.58092831498132</v>
+        <v>-17.96165735033968</v>
       </c>
       <c r="F87">
-        <v>1.545265398793788</v>
+        <v>2.195361509571617</v>
       </c>
       <c r="G87">
-        <v>-8.893524402159645</v>
+        <v>-8.525590861561755</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-19.72508939631608</v>
       </c>
       <c r="E88">
-        <v>-19.19581732120308</v>
+        <v>-18.50165788679389</v>
       </c>
       <c r="F88">
-        <v>1.801777648744683</v>
+        <v>2.298977017783391</v>
       </c>
       <c r="G88">
-        <v>-9.006214581690459</v>
+        <v>-8.071297806006722</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-19.39848946006498</v>
       </c>
       <c r="E89">
-        <v>-19.19106604744747</v>
+        <v>-19.36003945019813</v>
       </c>
       <c r="F89">
-        <v>2.014065019794918</v>
+        <v>2.585060327279423</v>
       </c>
       <c r="G89">
-        <v>-8.638546031668566</v>
+        <v>-7.974924780170367</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-19.11037910246031</v>
       </c>
       <c r="E90">
-        <v>-22.40031888952369</v>
+        <v>-21.82936862227686</v>
       </c>
       <c r="F90">
-        <v>1.510778807080439</v>
+        <v>2.283854342477883</v>
       </c>
       <c r="G90">
-        <v>-7.944619256956724</v>
+        <v>-6.953186387736863</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-18.86575967203231</v>
       </c>
       <c r="E91">
-        <v>-23.38482517444032</v>
+        <v>-23.26171153113843</v>
       </c>
       <c r="F91">
-        <v>1.758796977683028</v>
+        <v>2.043404136467271</v>
       </c>
       <c r="G91">
-        <v>-7.085843541900511</v>
+        <v>-7.038996340957574</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-18.67987510041012</v>
       </c>
       <c r="E92">
-        <v>-25.15085784719524</v>
+        <v>-25.54143414660476</v>
       </c>
       <c r="F92">
-        <v>1.159294234398581</v>
+        <v>2.272828772346622</v>
       </c>
       <c r="G92">
-        <v>-7.850471890884292</v>
+        <v>-7.05333977174115</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-18.55165212000701</v>
       </c>
       <c r="E93">
-        <v>-25.24749892151267</v>
+        <v>-26.27568452993252</v>
       </c>
       <c r="F93">
-        <v>1.917010181413316</v>
+        <v>1.928378695649337</v>
       </c>
       <c r="G93">
-        <v>-7.598873129266409</v>
+        <v>-6.978280864746643</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-18.4814306134439</v>
       </c>
       <c r="E94">
-        <v>-29.12536687174472</v>
+        <v>-28.8039353110766</v>
       </c>
       <c r="F94">
-        <v>1.525354759900099</v>
+        <v>2.204281369764963</v>
       </c>
       <c r="G94">
-        <v>-8.366804070157949</v>
+        <v>-6.998608122133051</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-18.45900934114146</v>
       </c>
       <c r="E95">
-        <v>-29.70078599437706</v>
+        <v>-30.64740045577162</v>
       </c>
       <c r="F95">
-        <v>1.569735371872485</v>
+        <v>1.829817885329446</v>
       </c>
       <c r="G95">
-        <v>-8.515180517504691</v>
+        <v>-7.022480770674191</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-18.46904074898713</v>
       </c>
       <c r="E96">
-        <v>-34.93658168955806</v>
+        <v>-32.72232199099367</v>
       </c>
       <c r="F96">
-        <v>1.133384558773818</v>
+        <v>1.881932135374369</v>
       </c>
       <c r="G96">
-        <v>-6.386388515516986</v>
+        <v>-7.267107538861506</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-18.49404890379371</v>
       </c>
       <c r="E97">
-        <v>-35.24167867008563</v>
+        <v>-35.15905468398949</v>
       </c>
       <c r="F97">
-        <v>0.6528651957578806</v>
+        <v>1.480634517292565</v>
       </c>
       <c r="G97">
-        <v>-7.095654720073915</v>
+        <v>-7.388648142556194</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-18.510589263096</v>
       </c>
       <c r="E98">
-        <v>-37.33701323896921</v>
+        <v>-36.31789616747712</v>
       </c>
       <c r="F98">
-        <v>1.126096582363988</v>
+        <v>1.327953151078171</v>
       </c>
       <c r="G98">
-        <v>-8.448179673690655</v>
+        <v>-7.47958037666467</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-18.50268629282445</v>
       </c>
       <c r="E99">
-        <v>-40.86812957569133</v>
+        <v>-38.99376038552825</v>
       </c>
       <c r="F99">
-        <v>1.010794466833519</v>
+        <v>1.189294388258368</v>
       </c>
       <c r="G99">
-        <v>-8.774954825809644</v>
+        <v>-7.440729886404313</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-18.45055719809909</v>
       </c>
       <c r="E100">
-        <v>-40.95557128692427</v>
+        <v>-42.1445733910528</v>
       </c>
       <c r="F100">
-        <v>0.7770855147468889</v>
+        <v>0.9349855955989195</v>
       </c>
       <c r="G100">
-        <v>-7.270488453106998</v>
+        <v>-7.258001261727703</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-18.35004579824074</v>
       </c>
       <c r="E101">
-        <v>-44.05347445677616</v>
+        <v>-43.48214209408745</v>
       </c>
       <c r="F101">
-        <v>0.6403502210363857</v>
+        <v>0.8704160132855036</v>
       </c>
       <c r="G101">
-        <v>-8.26283508293375</v>
+        <v>-7.418703034289091</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-18.19777443957588</v>
       </c>
       <c r="E102">
-        <v>-46.80951641945311</v>
+        <v>-45.8119451700114</v>
       </c>
       <c r="F102">
-        <v>0.1045149679637059</v>
+        <v>0.5380352496470076</v>
       </c>
       <c r="G102">
-        <v>-8.299268023702735</v>
+        <v>-7.88336988347691</v>
       </c>
     </row>
   </sheetData>
